--- a/src/views/game/zlzq/cardList/qieCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/qieCard/z_level.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11790" windowHeight="10800" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="14790" windowHeight="11415" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="港口" sheetId="6" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="70">
   <si>
     <t>名称</t>
   </si>
@@ -51,18 +51,12 @@
     <t>黑金勒索者</t>
   </si>
   <si>
-    <t>黑夜突袭</t>
-  </si>
-  <si>
     <t>酗酒醉汉</t>
   </si>
   <si>
     <t>不法交易</t>
   </si>
   <si>
-    <t>黑旗舰队飞斧手</t>
-  </si>
-  <si>
     <t>小计：</t>
   </si>
   <si>
@@ -96,6 +90,9 @@
     <t>赤影·艾希尔</t>
   </si>
   <si>
+    <t>魔卡幻术师·梅基</t>
+  </si>
+  <si>
     <t>钢之咆哮·布瑞恩</t>
   </si>
   <si>
@@ -126,6 +123,9 @@
     <t>绝望镰魔</t>
   </si>
   <si>
+    <t>破卵而出</t>
+  </si>
+  <si>
     <t>岩浆球</t>
   </si>
   <si>
@@ -138,9 +138,6 @@
     <t>夺魂死镰</t>
   </si>
   <si>
-    <t>恶灵魔焰</t>
-  </si>
-  <si>
     <t>痛苦之心</t>
   </si>
   <si>
@@ -156,24 +153,21 @@
     <t>炼狱卡等：</t>
   </si>
   <si>
-    <t>炫目神光</t>
-  </si>
-  <si>
     <t>田园守望者</t>
   </si>
   <si>
     <t>光明惩戒</t>
   </si>
   <si>
-    <t>传记·钢铁守卫</t>
-  </si>
-  <si>
     <t>四芒军旗1</t>
   </si>
   <si>
     <t>四芒军旗2</t>
   </si>
   <si>
+    <t>圣殿御卫</t>
+  </si>
+  <si>
     <t>白袍主教</t>
   </si>
   <si>
@@ -183,9 +177,6 @@
     <t>召集护卫</t>
   </si>
   <si>
-    <t>阳炎坠落</t>
-  </si>
-  <si>
     <t>曙光·安娜贝尔</t>
   </si>
   <si>
@@ -210,28 +201,28 @@
     <t>帝国卡等：</t>
   </si>
   <si>
-    <t>沉重否定</t>
+    <t>学仆-观测型</t>
+  </si>
+  <si>
+    <t>沉重否定1</t>
+  </si>
+  <si>
+    <t>沉重否定2</t>
   </si>
   <si>
     <t>全数否定</t>
   </si>
   <si>
-    <t>克隆术</t>
-  </si>
-  <si>
     <t>破魔系教授</t>
   </si>
   <si>
-    <t>咒术系学士</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型</t>
+    <t>克隆术1</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型1</t>
   </si>
   <si>
     <t>观星台大预言家</t>
-  </si>
-  <si>
-    <t>幻象巨龙</t>
   </si>
   <si>
     <t>米拉方舟</t>
@@ -1221,7 +1212,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1232,7 +1223,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1240,10 +1231,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1251,10 +1242,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1265,7 +1256,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1276,9 +1267,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -1287,9 +1278,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -1298,9 +1289,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -1309,43 +1300,43 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1">
-        <v>4</v>
-      </c>
-      <c r="C9" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+    <row r="9" spans="1:4">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1">
+        <f>AVERAGE(C2:C8)</f>
+        <v>20.8571428571429</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B14" s="2">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="C12" s="1">
-        <f>AVERAGE(C2:C9)</f>
-        <v>20.5</v>
-      </c>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
@@ -1354,12 +1345,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2">
         <v>22</v>
@@ -1367,36 +1358,30 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="2">
-        <v>5</v>
-      </c>
-      <c r="C19" s="2">
-        <v>21</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2"/>
@@ -1404,64 +1389,70 @@
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="2">
-        <f>AVERAGE(C15:C19)</f>
-        <v>21.2</v>
+      <c r="A21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="2">
+        <f>AVERAGE(C14:C18)</f>
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="3">
+        <v>2</v>
+      </c>
+      <c r="C24" s="3">
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B26" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B27" s="3">
         <v>4</v>
       </c>
       <c r="C27" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B28" s="3">
         <v>5</v>
       </c>
       <c r="C28" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1476,26 +1467,26 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C31" s="3">
-        <f>AVERAGE(C25:C28)</f>
-        <v>20</v>
+        <f>AVERAGE(C24:C28)</f>
+        <v>19.8</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>24</v>
-      </c>
       <c r="C34" s="4">
-        <f>AVERAGE(C2:C9,C15:C19,C25:C28)</f>
-        <v>20.5882352941176</v>
+        <f>AVERAGE(C2:C8,C14:C18,C24:C28)</f>
+        <v>20.7058823529412</v>
       </c>
     </row>
   </sheetData>
@@ -1515,7 +1506,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1526,9 +1517,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -1537,9 +1528,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -1548,9 +1539,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1">
         <v>4</v>
@@ -1559,22 +1550,22 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C7" s="1">
         <f>AVERAGE(C2:C4)</f>
@@ -1582,9 +1573,9 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2">
         <v>2</v>
@@ -1593,9 +1584,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2">
         <v>2</v>
@@ -1604,9 +1595,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2">
         <v>3</v>
@@ -1615,59 +1606,59 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="2">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B15" s="2">
         <v>4</v>
       </c>
-      <c r="C14" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
+      <c r="C15" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="B15" s="2">
-        <v>5</v>
-      </c>
-      <c r="C15" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="B16" s="2">
         <v>5</v>
       </c>
       <c r="C16" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1682,19 +1673,19 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C20" s="2">
         <f>AVERAGE(C10:C17)</f>
-        <v>20.625</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" s="3">
         <v>2</v>
@@ -1705,35 +1696,35 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="3">
         <v>3</v>
       </c>
       <c r="C24" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="3">
         <v>5</v>
       </c>
       <c r="C25" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B26" s="3">
         <v>6</v>
       </c>
       <c r="C26" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1748,26 +1739,26 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C23:C26)</f>
-        <v>17.25</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C4,C10:C17,C23:C26)</f>
-        <v>20</v>
+        <v>20.6666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1779,7 +1770,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1787,7 +1778,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1798,98 +1789,98 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="1">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="1">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="B3" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="1">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="1">
-        <f>AVERAGE(C2:C4)</f>
-        <v>20</v>
-      </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="10" spans="1:3">
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1">
+        <f>AVERAGE(C2:C3)</f>
+        <v>22</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2">
         <v>1</v>
       </c>
       <c r="C10" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="2">
-        <v>1</v>
-      </c>
-      <c r="C11" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="2">
+        <v>3</v>
+      </c>
+      <c r="C12" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B12" s="2">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
@@ -1898,179 +1889,155 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="2">
+        <v>4</v>
+      </c>
+      <c r="C14" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="2">
+        <f>AVERAGE(C9:C14)</f>
+        <v>20.6666666666667</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B20" s="3">
         <v>3</v>
       </c>
-      <c r="C14" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
+      <c r="C20" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B21" s="3">
         <v>4</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C21" s="3">
         <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="2">
-        <v>4</v>
-      </c>
-      <c r="C16" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="2">
-        <f>AVERAGE(C10:C16)</f>
-        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B22" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B23" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B24" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C24" s="3">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B25" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C25" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="3">
+        <v>8</v>
+      </c>
+      <c r="C26" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="3">
+        <f>AVERAGE(C20:C26)</f>
+        <v>19.1428571428571</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B26" s="3">
-        <v>6</v>
-      </c>
-      <c r="C26" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="3">
-        <v>7</v>
-      </c>
-      <c r="C27" s="3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B28" s="3">
-        <v>8</v>
-      </c>
-      <c r="C28" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" s="3">
-        <f>AVERAGE(C22:C28)</f>
-        <v>17.7142857142857</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C34" s="4">
-        <f>AVERAGE(C2:C4,C10:C16,C22:C28)</f>
-        <v>19.0588235294118</v>
+      <c r="C32" s="4">
+        <f>AVERAGE(C2:C3,C9:C14,C20:C26)</f>
+        <v>20.1333333333333</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C34 C7" formulaRange="1"/>
+    <ignoredError sqref="C6 C32" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2086,7 +2053,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2097,20 +2064,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -2119,112 +2086,112 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C8" s="1">
         <f>AVERAGE(C2:C5)</f>
-        <v>12.75</v>
+        <v>14.75</v>
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B11" s="2">
         <v>2</v>
       </c>
       <c r="C11" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B13" s="2">
         <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B14" s="2">
         <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B15" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C15" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B16" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="2">
         <v>12</v>
@@ -2232,13 +2199,13 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B17" s="2">
         <v>7</v>
       </c>
       <c r="C17" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2253,52 +2220,52 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C20" s="2">
         <f>AVERAGE(C11:C17)</f>
-        <v>13.1428571428571</v>
+        <v>14.2857142857143</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B23" s="3">
         <v>3</v>
       </c>
       <c r="C23" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B24" s="3">
         <v>4</v>
       </c>
       <c r="C24" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B25" s="3">
         <v>5</v>
       </c>
       <c r="C25" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B26" s="3">
         <v>7</v>
@@ -2319,26 +2286,26 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C23:C26)</f>
-        <v>12.75</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C5,C11:C17,C23:C26)</f>
-        <v>12.9333333333333</v>
+        <v>15.0666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/src/views/game/zlzq/cardList/qieCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/qieCard/z_level.xlsx
@@ -1,14 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\code\keyuanWeb\src\views\game\zlzq\cardList\qieCard\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14790" windowHeight="11415" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="13665" windowHeight="9975" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="港口" sheetId="6" r:id="rId1"/>
-    <sheet name="炼狱" sheetId="8" r:id="rId2"/>
+    <sheet name="炼狱" sheetId="8" r:id="rId1"/>
+    <sheet name="港口" sheetId="6" r:id="rId2"/>
     <sheet name="帝国" sheetId="5" r:id="rId3"/>
     <sheet name="隐秘" sheetId="9" r:id="rId4"/>
     <sheet name="企鹅" sheetId="10" r:id="rId5"/>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="73">
   <si>
     <t>名称</t>
   </si>
@@ -42,13 +47,79 @@
     <t>卡等</t>
   </si>
   <si>
-    <t>心灵黑洞</t>
-  </si>
-  <si>
-    <t>狡诈学徒</t>
-  </si>
-  <si>
-    <t>黑金勒索者</t>
+    <t>冥河守卫1</t>
+  </si>
+  <si>
+    <t>冥河守卫2</t>
+  </si>
+  <si>
+    <t>落雷击</t>
+  </si>
+  <si>
+    <t>烈焰风暴</t>
+  </si>
+  <si>
+    <t>小计：</t>
+  </si>
+  <si>
+    <t>蓝色卡等：</t>
+  </si>
+  <si>
+    <t>碎颅魔</t>
+  </si>
+  <si>
+    <t>绝望镰魔</t>
+  </si>
+  <si>
+    <t>破卵而出</t>
+  </si>
+  <si>
+    <t>符文·致命甲壳</t>
+  </si>
+  <si>
+    <t>岩浆球</t>
+  </si>
+  <si>
+    <t>灼神双炎</t>
+  </si>
+  <si>
+    <t>雷光炼狱</t>
+  </si>
+  <si>
+    <t>紫色卡等：</t>
+  </si>
+  <si>
+    <t>痛苦之心</t>
+  </si>
+  <si>
+    <t>血影</t>
+  </si>
+  <si>
+    <t>怨魂饕餮兽</t>
+  </si>
+  <si>
+    <t>血翼·莉莉丝</t>
+  </si>
+  <si>
+    <t>橙色卡等：</t>
+  </si>
+  <si>
+    <t>总计：</t>
+  </si>
+  <si>
+    <t>炼狱卡等：</t>
+  </si>
+  <si>
+    <t>心灵黑洞1</t>
+  </si>
+  <si>
+    <t>心灵黑洞2</t>
+  </si>
+  <si>
+    <t>黑金勒索者1</t>
+  </si>
+  <si>
+    <t>黑金勒索者2</t>
   </si>
   <si>
     <t>酗酒醉汉</t>
@@ -57,10 +128,7 @@
     <t>不法交易</t>
   </si>
   <si>
-    <t>小计：</t>
-  </si>
-  <si>
-    <t>蓝色卡等：</t>
+    <t>热血矿工</t>
   </si>
   <si>
     <t>海燕精卫</t>
@@ -72,15 +140,9 @@
     <t>黑水伏击</t>
   </si>
   <si>
-    <t>黑金诈术师</t>
-  </si>
-  <si>
     <t>星辰陨落</t>
   </si>
   <si>
-    <t>紫色卡等：</t>
-  </si>
-  <si>
     <t>花剑绅士·翔</t>
   </si>
   <si>
@@ -96,61 +158,10 @@
     <t>钢之咆哮·布瑞恩</t>
   </si>
   <si>
-    <t>橙色卡等：</t>
-  </si>
-  <si>
-    <t>总计：</t>
-  </si>
-  <si>
     <t>港口卡等：</t>
   </si>
   <si>
-    <t>冥河守卫</t>
-  </si>
-  <si>
-    <t>落雷击</t>
-  </si>
-  <si>
-    <t>烈焰风暴</t>
-  </si>
-  <si>
-    <t>碎颅魔</t>
-  </si>
-  <si>
-    <t>觅食大嘴兽</t>
-  </si>
-  <si>
-    <t>绝望镰魔</t>
-  </si>
-  <si>
-    <t>破卵而出</t>
-  </si>
-  <si>
-    <t>岩浆球</t>
-  </si>
-  <si>
-    <t>灼神双炎</t>
-  </si>
-  <si>
-    <t>雷光炼狱</t>
-  </si>
-  <si>
-    <t>夺魂死镰</t>
-  </si>
-  <si>
-    <t>痛苦之心</t>
-  </si>
-  <si>
-    <t>血影</t>
-  </si>
-  <si>
-    <t>怨魂饕餮兽</t>
-  </si>
-  <si>
-    <t>血翼·莉莉丝</t>
-  </si>
-  <si>
-    <t>炼狱卡等：</t>
+    <t>增援战线</t>
   </si>
   <si>
     <t>田园守望者</t>
@@ -159,21 +170,18 @@
     <t>光明惩戒</t>
   </si>
   <si>
-    <t>四芒军旗1</t>
-  </si>
-  <si>
-    <t>四芒军旗2</t>
-  </si>
-  <si>
-    <t>圣殿御卫</t>
+    <t>四芒军旗</t>
+  </si>
+  <si>
+    <t>传记·钢铁守卫</t>
+  </si>
+  <si>
+    <t>圣殿骑士</t>
   </si>
   <si>
     <t>白袍主教</t>
   </si>
   <si>
-    <t>圣殿骑士</t>
-  </si>
-  <si>
     <t>召集护卫</t>
   </si>
   <si>
@@ -183,6 +191,9 @@
     <t>圣枪·卡洛琳</t>
   </si>
   <si>
+    <t>符文·辉煌赞美诗</t>
+  </si>
+  <si>
     <t>明日之音·露娜</t>
   </si>
   <si>
@@ -192,42 +203,48 @@
     <t>正阳大主教·伊恩</t>
   </si>
   <si>
-    <t>炫目天使·蕾娜</t>
-  </si>
-  <si>
     <t>钢铁统帅·雷蒙德</t>
   </si>
   <si>
     <t>帝国卡等：</t>
   </si>
   <si>
-    <t>学仆-观测型</t>
-  </si>
-  <si>
     <t>沉重否定1</t>
   </si>
   <si>
     <t>沉重否定2</t>
   </si>
   <si>
+    <t>符文·静默进军</t>
+  </si>
+  <si>
     <t>全数否定</t>
   </si>
   <si>
+    <t>隐形术</t>
+  </si>
+  <si>
     <t>破魔系教授</t>
   </si>
   <si>
     <t>克隆术1</t>
   </si>
   <si>
+    <t>克隆术2</t>
+  </si>
+  <si>
     <t>学仆-脉冲型1</t>
   </si>
   <si>
-    <t>观星台大预言家</t>
+    <t>学仆-脉冲型2</t>
   </si>
   <si>
     <t>米拉方舟</t>
   </si>
   <si>
+    <t>心灵操控</t>
+  </si>
+  <si>
     <t>No.5咒刃·布雷克</t>
   </si>
   <si>
@@ -235,9 +252,6 @@
   </si>
   <si>
     <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>No.6沃凡瑞拉</t>
   </si>
   <si>
     <t>隐秘卡等：</t>
@@ -1204,300 +1218,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="16.375" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="11.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1">
-        <f>AVERAGE(C2:C8)</f>
-        <v>20.8571428571429</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="2">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2">
-        <v>2</v>
-      </c>
-      <c r="C15" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2">
-        <v>3</v>
-      </c>
-      <c r="C16" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="2">
-        <v>4</v>
-      </c>
-      <c r="C17" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="2">
-        <v>5</v>
-      </c>
-      <c r="C18" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="2">
-        <f>AVERAGE(C14:C18)</f>
-        <v>21.4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" s="3">
-        <v>2</v>
-      </c>
-      <c r="C24" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" s="3">
-        <v>3</v>
-      </c>
-      <c r="C25" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" s="3">
-        <v>4</v>
-      </c>
-      <c r="C26" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" s="3">
-        <v>4</v>
-      </c>
-      <c r="C27" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28" s="3">
-        <v>5</v>
-      </c>
-      <c r="C28" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C31" s="3">
-        <f>AVERAGE(C24:C28)</f>
-        <v>19.8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C34" s="4">
-        <f>AVERAGE(C2:C8,C14:C18,C24:C28)</f>
-        <v>20.7058823529412</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
@@ -1519,41 +1239,47 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1">
         <v>4</v>
       </c>
-      <c r="C4" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1">
+        <v>24</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1"/>
@@ -1561,104 +1287,98 @@
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="1">
-        <f>AVERAGE(C2:C4)</f>
-        <v>22</v>
-      </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="2">
-        <v>2</v>
-      </c>
-      <c r="C10" s="2">
-        <v>22</v>
-      </c>
+      <c r="C8" s="1">
+        <f>AVERAGE(C2:C5)</f>
+        <v>23.75</v>
+      </c>
+      <c r="D8" s="2"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2">
         <v>2</v>
       </c>
       <c r="C11" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2">
         <v>3</v>
       </c>
       <c r="C12" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2">
         <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2">
         <v>5</v>
       </c>
       <c r="C17" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1673,19 +1393,19 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="2">
-        <f>AVERAGE(C10:C17)</f>
-        <v>21.25</v>
+        <f>AVERAGE(C11:C17)</f>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="B23" s="3">
         <v>2</v>
@@ -1696,35 +1416,35 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="B24" s="3">
         <v>3</v>
       </c>
       <c r="C24" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="B25" s="3">
         <v>5</v>
       </c>
       <c r="C25" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B26" s="3">
         <v>6</v>
       </c>
       <c r="C26" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1739,14 +1459,14 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C23:C26)</f>
-        <v>18.5</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1754,11 +1474,294 @@
         <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="4">
+        <f>AVERAGE(C2:C5,C11:C17,C23:C26)</f>
+        <v>22.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1">
+        <f>AVERAGE(C2:C8)</f>
+        <v>22</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="2">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="2">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C14:C17)</f>
+        <v>22.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="3">
+        <v>2</v>
+      </c>
+      <c r="C23" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="3">
+        <v>3</v>
+      </c>
+      <c r="C24" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3">
+        <v>4</v>
+      </c>
+      <c r="C25" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3">
+        <v>4</v>
+      </c>
+      <c r="C26" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="4">
-        <f>AVERAGE(C2:C4,C10:C17,C23:C26)</f>
-        <v>20.6666666666667</v>
+      <c r="B27" s="3">
+        <v>5</v>
+      </c>
+      <c r="C27" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="3">
+        <f>AVERAGE(C23:C27)</f>
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="4">
+        <f>AVERAGE(C2:C8,C14:C17,C23:C27)</f>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1791,30 +1794,36 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1">
         <v>3</v>
       </c>
       <c r="C2" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="1">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="1">
         <v>5</v>
       </c>
-      <c r="C3" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
+      <c r="C4" s="1">
+        <v>19</v>
+      </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1"/>
@@ -1822,65 +1831,59 @@
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="1">
-        <f>AVERAGE(C2:C3)</f>
+      <c r="C7" s="1">
+        <f>AVERAGE(C2:C4)</f>
         <v>22</v>
       </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="2">
-        <v>1</v>
-      </c>
-      <c r="C9" s="2">
-        <v>18</v>
-      </c>
+      <c r="D7" s="2"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2">
         <v>1</v>
       </c>
       <c r="C10" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="2">
         <v>3</v>
       </c>
       <c r="C12" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
@@ -1891,7 +1894,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
@@ -1912,91 +1915,91 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" s="2">
-        <f>AVERAGE(C9:C14)</f>
-        <v>20.6666666666667</v>
+        <f>AVERAGE(C10:C14)</f>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20" s="3">
         <v>3</v>
       </c>
       <c r="C20" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B21" s="3">
         <v>4</v>
       </c>
       <c r="C21" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" s="3">
         <v>4</v>
       </c>
       <c r="C22" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B23" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" s="3">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B24" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B25" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B26" s="3">
         <v>8</v>
       </c>
       <c r="C26" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2011,14 +2014,14 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C20:C26)</f>
-        <v>19.1428571428571</v>
+        <v>19.7142857142857</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2026,18 +2029,18 @@
         <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C3,C9:C14,C20:C26)</f>
-        <v>20.1333333333333</v>
+        <f>AVERAGE(C2:C4,C10:C14,C20:C26)</f>
+        <v>20.9333333333333</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C6 C32" formulaRange="1"/>
+    <ignoredError sqref="C32 C7" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2066,46 +2069,46 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2120,23 +2123,23 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="C8" s="1">
         <f>AVERAGE(C2:C5)</f>
-        <v>14.75</v>
+        <v>12</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="2">
         <v>12</v>
@@ -2144,74 +2147,80 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B13" s="2">
         <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B15" s="2">
         <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B16" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B17" s="2">
         <v>7</v>
       </c>
       <c r="C17" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="2">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2"/>
@@ -2219,34 +2228,28 @@
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="2">
-        <f>AVERAGE(C11:C17)</f>
-        <v>14.2857142857143</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B23" s="3">
-        <v>3</v>
-      </c>
-      <c r="C23" s="3">
-        <v>19</v>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="2">
+        <f>AVERAGE(C11:C18)</f>
+        <v>14.875</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B24" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24" s="3">
         <v>20</v>
@@ -2254,24 +2257,24 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B25" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B26" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2286,14 +2289,14 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C23:C26)</f>
-        <v>16.75</v>
+        <f>AVERAGE(C24:C26)</f>
+        <v>19.3333333333333</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2301,11 +2304,11 @@
         <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C5,C11:C17,C23:C26)</f>
-        <v>15.0666666666667</v>
+        <f>AVERAGE(C2:C5,C11:C18,C24:C26)</f>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
